--- a/ig/ch-elm/StructureDefinition-ch-elm-humanname.xlsx
+++ b/ig/ch-elm/StructureDefinition-ch-elm-humanname.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.13.1</t>
+    <t>1.14.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-21T11:21:00+00:00</t>
+    <t>2026-05-26T14:58:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -360,7 +360,7 @@
     <t>CH ELM Extension: VCT Code</t>
   </si>
   <si>
-    <t>This CH ELM extension enables to provide the VCT Code.</t>
+    <t>This CH ELM extension enables to provide the VCT Code. Retired. Ues identifier instead (see Guidance)</t>
   </si>
   <si>
     <t>HumanName.extension:hivcode</t>
@@ -512,7 +512,7 @@
     <t>dataabsentreason</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {data-absent-reason}
+    <t xml:space="preserve">Extension {data-absent-reason|5.3.0}
 </t>
   </si>
   <si>
@@ -629,7 +629,7 @@
     <t>salutationandtitle</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {iso21090-EN-qualifier|5.2.0}
+    <t xml:space="preserve">Extension {iso21090-EN-qualifier|5.3.0-ballot-tc1}
 </t>
   </si>
   <si>
@@ -3739,7 +3739,7 @@
         <v>80</v>
       </c>
       <c r="AI24" t="s" s="2">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="AJ24" t="s" s="2">
         <v>107</v>

--- a/ig/ch-elm/StructureDefinition-ch-elm-humanname.xlsx
+++ b/ig/ch-elm/StructureDefinition-ch-elm-humanname.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.14.0</t>
+    <t>1.14.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-26T14:58:40+00:00</t>
+    <t>2026-07-01T19:23:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/ch-elm/StructureDefinition-ch-elm-humanname.xlsx
+++ b/ig/ch-elm/StructureDefinition-ch-elm-humanname.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.14.1</t>
+    <t>1.15.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-01T19:23:08+00:00</t>
+    <t>2026-08-12T07:20:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/ch-elm/StructureDefinition-ch-elm-humanname.xlsx
+++ b/ig/ch-elm/StructureDefinition-ch-elm-humanname.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.15.0</t>
+    <t>1.15.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-12T07:20:00+00:00</t>
+    <t>2026-08-14T07:34:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
